--- a/Data/Excel/world_cost.xlsx
+++ b/Data/Excel/world_cost.xlsx
@@ -166,13 +166,13 @@
     </row>
     <row r="5">
       <c r="B5">
-        <v>20020101</v>
+        <v>30910001</v>
       </c>
       <c r="C5">
-        <v>200201</v>
+        <v>30901001</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -180,13 +180,13 @@
     </row>
     <row r="6">
       <c r="B6">
-        <v>20020102</v>
+        <v>30910002</v>
       </c>
       <c r="C6">
-        <v>200201</v>
+        <v>30901001</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E6">
         <v>20</v>
@@ -194,13 +194,13 @@
     </row>
     <row r="7">
       <c r="B7">
-        <v>20020103</v>
+        <v>30910003</v>
       </c>
       <c r="C7">
-        <v>200201</v>
+        <v>30901001</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>20000002</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -208,13 +208,13 @@
     </row>
     <row r="8">
       <c r="B8">
-        <v>20030101</v>
+        <v>30910004</v>
       </c>
       <c r="C8">
-        <v>200301</v>
+        <v>30901002</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="E8">
         <v>50</v>
@@ -222,13 +222,13 @@
     </row>
     <row r="9">
       <c r="B9">
-        <v>20030102</v>
+        <v>30910005</v>
       </c>
       <c r="C9">
-        <v>200301</v>
+        <v>30901002</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -236,13 +236,13 @@
     </row>
     <row r="10">
       <c r="B10">
-        <v>20040101</v>
+        <v>30910006</v>
       </c>
       <c r="C10">
-        <v>200401</v>
+        <v>30901003</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -250,13 +250,13 @@
     </row>
     <row r="11">
       <c r="B11">
-        <v>20040102</v>
+        <v>30910007</v>
       </c>
       <c r="C11">
-        <v>200401</v>
+        <v>30901003</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E11">
         <v>30</v>
@@ -264,13 +264,13 @@
     </row>
     <row r="12">
       <c r="B12">
-        <v>20050101</v>
+        <v>30910008</v>
       </c>
       <c r="C12">
-        <v>200501</v>
+        <v>30901004</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="E12">
         <v>120</v>
@@ -278,13 +278,13 @@
     </row>
     <row r="13">
       <c r="B13">
-        <v>20050102</v>
+        <v>30910009</v>
       </c>
       <c r="C13">
-        <v>200501</v>
+        <v>30901004</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>20000002</v>
       </c>
       <c r="E13">
         <v>30</v>
@@ -292,13 +292,13 @@
     </row>
     <row r="14">
       <c r="B14">
-        <v>20060101</v>
+        <v>30910010</v>
       </c>
       <c r="C14">
-        <v>200601</v>
+        <v>30901005</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="E14">
         <v>200</v>
@@ -306,13 +306,13 @@
     </row>
     <row r="15">
       <c r="B15">
-        <v>20060102</v>
+        <v>30910011</v>
       </c>
       <c r="C15">
-        <v>200601</v>
+        <v>30901005</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E15">
         <v>20</v>
@@ -320,13 +320,13 @@
     </row>
     <row r="16">
       <c r="B16">
-        <v>20060103</v>
+        <v>30910012</v>
       </c>
       <c r="C16">
-        <v>200601</v>
+        <v>30901005</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>20000002</v>
       </c>
       <c r="E16">
         <v>20</v>
@@ -334,13 +334,13 @@
     </row>
     <row r="17">
       <c r="B17">
-        <v>20060104</v>
+        <v>30910013</v>
       </c>
       <c r="C17">
-        <v>200601</v>
+        <v>30901005</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>20000005</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -348,13 +348,13 @@
     </row>
     <row r="18">
       <c r="B18">
-        <v>20070101</v>
+        <v>30910014</v>
       </c>
       <c r="C18">
-        <v>200701</v>
+        <v>30901006</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="E18">
         <v>150</v>
@@ -362,13 +362,13 @@
     </row>
     <row r="19">
       <c r="B19">
-        <v>20070102</v>
+        <v>30910015</v>
       </c>
       <c r="C19">
-        <v>200701</v>
+        <v>30901006</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E19">
         <v>25</v>
@@ -376,13 +376,13 @@
     </row>
     <row r="20">
       <c r="B20">
-        <v>20070103</v>
+        <v>30910016</v>
       </c>
       <c r="C20">
-        <v>200701</v>
+        <v>30901006</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>20000002</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -390,13 +390,13 @@
     </row>
     <row r="21">
       <c r="B21">
-        <v>20110101</v>
+        <v>30910017</v>
       </c>
       <c r="C21">
-        <v>201101</v>
+        <v>30901007</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -404,13 +404,13 @@
     </row>
     <row r="22">
       <c r="B22">
-        <v>20110102</v>
+        <v>30910018</v>
       </c>
       <c r="C22">
-        <v>201101</v>
+        <v>30901007</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -418,13 +418,13 @@
     </row>
     <row r="23">
       <c r="B23">
-        <v>20120101</v>
+        <v>30910019</v>
       </c>
       <c r="C23">
-        <v>201201</v>
+        <v>30901008</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="E23">
         <v>15</v>
@@ -432,13 +432,13 @@
     </row>
     <row r="24">
       <c r="B24">
-        <v>20120102</v>
+        <v>30910020</v>
       </c>
       <c r="C24">
-        <v>201201</v>
+        <v>30901008</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -446,13 +446,13 @@
     </row>
     <row r="25">
       <c r="B25">
-        <v>20130101</v>
+        <v>30910021</v>
       </c>
       <c r="C25">
-        <v>201301</v>
+        <v>30901009</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="E25">
         <v>15</v>
@@ -460,13 +460,13 @@
     </row>
     <row r="26">
       <c r="B26">
-        <v>20130102</v>
+        <v>30910022</v>
       </c>
       <c r="C26">
-        <v>201301</v>
+        <v>30901009</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -474,13 +474,13 @@
     </row>
     <row r="27">
       <c r="B27">
-        <v>20210101</v>
+        <v>30910023</v>
       </c>
       <c r="C27">
-        <v>202101</v>
+        <v>30901010</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -488,13 +488,13 @@
     </row>
     <row r="28">
       <c r="B28">
-        <v>20210102</v>
+        <v>30910024</v>
       </c>
       <c r="C28">
-        <v>202101</v>
+        <v>30901010</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E28">
         <v>15</v>
@@ -502,13 +502,13 @@
     </row>
     <row r="29">
       <c r="B29">
-        <v>20220101</v>
+        <v>30910025</v>
       </c>
       <c r="C29">
-        <v>202201</v>
+        <v>30901011</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="E29">
         <v>180</v>
@@ -516,13 +516,13 @@
     </row>
     <row r="30">
       <c r="B30">
-        <v>20220102</v>
+        <v>30910026</v>
       </c>
       <c r="C30">
-        <v>202201</v>
+        <v>30901011</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E30">
         <v>20</v>
@@ -530,13 +530,13 @@
     </row>
     <row r="31">
       <c r="B31">
-        <v>20220103</v>
+        <v>30910027</v>
       </c>
       <c r="C31">
-        <v>202201</v>
+        <v>30901011</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>20000002</v>
       </c>
       <c r="E31">
         <v>20</v>
@@ -544,13 +544,13 @@
     </row>
     <row r="32">
       <c r="B32">
-        <v>20230101</v>
+        <v>30910028</v>
       </c>
       <c r="C32">
-        <v>202301</v>
+        <v>30901012</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="E32">
         <v>250</v>
@@ -558,13 +558,13 @@
     </row>
     <row r="33">
       <c r="B33">
-        <v>20230102</v>
+        <v>30910029</v>
       </c>
       <c r="C33">
-        <v>202301</v>
+        <v>30901012</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>20000001</v>
       </c>
       <c r="E33">
         <v>20</v>
@@ -572,13 +572,13 @@
     </row>
     <row r="34">
       <c r="B34">
-        <v>20230103</v>
+        <v>30910030</v>
       </c>
       <c r="C34">
-        <v>202301</v>
+        <v>30901012</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>20000002</v>
       </c>
       <c r="E34">
         <v>30</v>

--- a/Data/Excel/world_cost.xlsx
+++ b/Data/Excel/world_cost.xlsx
@@ -52,8 +52,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -214,10 +214,10 @@
         <v>30901002</v>
       </c>
       <c r="D8">
-        <v>20000003</v>
+        <v>20000001</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -228,10 +228,10 @@
         <v>30901002</v>
       </c>
       <c r="D9">
-        <v>20000001</v>
+        <v>20000002</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -584,6 +584,34 @@
         <v>30</v>
       </c>
     </row>
+    <row r="35">
+      <c r="B35">
+        <v>30910031</v>
+      </c>
+      <c r="C35">
+        <v>30901013</v>
+      </c>
+      <c r="D35">
+        <v>20000001</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36">
+        <v>30910032</v>
+      </c>
+      <c r="C36">
+        <v>30901013</v>
+      </c>
+      <c r="D36">
+        <v>20000002</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>